--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="R34" t="n">
-        <v>4.84</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="R38" t="n">
-        <v>2.78</v>
+        <v>4.84</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="R36" t="n">
-        <v>4.93</v>
+        <v>2.78</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI67"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,245 +498,175 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_H</t>
+          <t>status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_A</t>
+          <t>Odd_H_FT</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Odd_D_FT</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_FT</t>
+          <t>Odd_A_FT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_FT</t>
+          <t>Odd_H_HT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_FT</t>
+          <t>Odd_D_HT</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Under25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under45</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>MinGolsH</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>MinGolsA</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_A</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_D</t>
+          <t>ChutegolH</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_D</t>
+          <t>ChutegolA</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_A</t>
+          <t>ChuteTotalH</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_75</t>
+          <t>ChuteTotalA</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_85</t>
+          <t>XGHome</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_95</t>
+          <t>XGAway</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_105</t>
+          <t>AtaquePerigosoH</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_115</t>
+          <t>AtaquePerigosoA</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_75</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_85</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_95</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_105</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_115</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_1</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_2</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over05</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over15</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under05</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under15</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under25</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -789,16 +719,16 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>-1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -854,11 +784,15 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -870,16 +804,16 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -893,49 +827,7 @@
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46171.27083333334</v>
       </c>
     </row>
@@ -986,16 +878,16 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>-1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -1051,11 +943,15 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1067,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1090,49 +986,7 @@
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="3" t="n">
+      <c r="AU3" s="3" t="n">
         <v>46171.29166666666</v>
       </c>
     </row>
@@ -1183,16 +1037,16 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>-1</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1248,11 +1102,15 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1264,16 +1122,16 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1287,49 +1145,7 @@
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="3" t="n">
+      <c r="AU4" s="3" t="n">
         <v>46171.33333333334</v>
       </c>
     </row>
@@ -1380,16 +1196,16 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>-1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1445,11 +1261,15 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -1461,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1484,49 +1304,7 @@
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3" t="n">
+      <c r="AU5" s="3" t="n">
         <v>46171.33333333334</v>
       </c>
     </row>
@@ -1577,16 +1355,16 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>-1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1642,11 +1420,15 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1658,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1681,49 +1463,7 @@
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="3" t="n">
+      <c r="AU6" s="3" t="n">
         <v>46171.35416666666</v>
       </c>
     </row>
@@ -1774,16 +1514,16 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1839,11 +1579,15 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1855,16 +1599,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1878,49 +1622,7 @@
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3" t="n">
+      <c r="AU7" s="3" t="n">
         <v>46171.35763888889</v>
       </c>
     </row>
@@ -1971,16 +1673,16 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2036,11 +1738,15 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2052,16 +1758,16 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2075,49 +1781,7 @@
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="3" t="n">
+      <c r="AU8" s="3" t="n">
         <v>46171.375</v>
       </c>
     </row>
@@ -2168,16 +1832,16 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-1</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2233,11 +1897,15 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -2249,16 +1917,16 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -2272,49 +1940,7 @@
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="3" t="n">
+      <c r="AU9" s="3" t="n">
         <v>46171.41666666666</v>
       </c>
     </row>
@@ -2365,16 +1991,16 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>-1</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2430,11 +2056,15 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -2446,16 +2076,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -2469,49 +2099,7 @@
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="3" t="n">
+      <c r="AU10" s="3" t="n">
         <v>46171.5</v>
       </c>
     </row>
@@ -2526,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2562,16 +2150,16 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>-1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -2627,11 +2215,15 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2643,16 +2235,16 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2666,49 +2258,7 @@
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="3" t="n">
+      <c r="AU11" s="3" t="n">
         <v>46171.5</v>
       </c>
     </row>
@@ -2723,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2759,16 +2309,16 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>-1</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2824,11 +2374,15 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2840,16 +2394,16 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2863,49 +2417,7 @@
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3" t="n">
+      <c r="AU12" s="3" t="n">
         <v>46171.5</v>
       </c>
     </row>
@@ -2920,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2956,16 +2468,16 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
-        <v>-1</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -3021,11 +2533,15 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -3037,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -3060,49 +2576,7 @@
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="3" t="n">
+      <c r="AU13" s="3" t="n">
         <v>46171.54166666666</v>
       </c>
     </row>
@@ -3117,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3153,16 +2627,16 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>-1</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -3218,11 +2692,15 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -3234,16 +2712,16 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3257,49 +2735,7 @@
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="3" t="n">
+      <c r="AU14" s="3" t="n">
         <v>46171.54166666666</v>
       </c>
     </row>
@@ -3314,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3350,16 +2786,16 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="n">
-        <v>-1</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -3415,11 +2851,15 @@
       <c r="AG15" t="n">
         <v>0</v>
       </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -3431,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3454,49 +2894,7 @@
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="3" t="n">
+      <c r="AU15" s="3" t="n">
         <v>46171.54166666666</v>
       </c>
     </row>
@@ -3521,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3547,16 +2945,16 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="n">
-        <v>-1</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -3612,11 +3010,15 @@
       <c r="AG16" t="n">
         <v>0</v>
       </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -3628,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -3651,49 +3053,7 @@
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="3" t="n">
+      <c r="AU16" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -3718,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3744,16 +3104,16 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="n">
-        <v>-1</v>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -3809,11 +3169,15 @@
       <c r="AG17" t="n">
         <v>0</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
@@ -3825,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3848,49 +3212,7 @@
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" s="3" t="n">
+      <c r="AU17" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -3905,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3941,16 +3263,16 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>-1</v>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
       </c>
       <c r="N18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4006,11 +3328,15 @@
       <c r="AG18" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -4022,16 +3348,16 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -4045,49 +3371,7 @@
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" s="3" t="n">
+      <c r="AU18" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -4102,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4138,16 +3422,16 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="n">
-        <v>-1</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -4203,11 +3487,15 @@
       <c r="AG19" t="n">
         <v>0</v>
       </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -4219,16 +3507,16 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4242,49 +3530,7 @@
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" s="3" t="n">
+      <c r="AU19" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -4299,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4335,16 +3581,16 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>-1</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -4400,11 +3646,15 @@
       <c r="AG20" t="n">
         <v>0</v>
       </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
@@ -4416,16 +3666,16 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -4439,49 +3689,7 @@
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" s="3" t="n">
+      <c r="AU20" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -4496,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4532,16 +3740,16 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
-      <c r="M21" t="n">
-        <v>-1</v>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -4597,11 +3805,15 @@
       <c r="AG21" t="n">
         <v>0</v>
       </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
@@ -4613,16 +3825,16 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -4636,49 +3848,7 @@
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" s="3" t="n">
+      <c r="AU21" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -4703,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4729,16 +3899,16 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" t="n">
-        <v>-1</v>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -4794,11 +3964,15 @@
       <c r="AG22" t="n">
         <v>0</v>
       </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -4810,16 +3984,16 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -4833,49 +4007,7 @@
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" s="3" t="n">
+      <c r="AU22" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -4900,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4926,16 +4058,16 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>-1</v>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -4991,11 +4123,15 @@
       <c r="AG23" t="n">
         <v>0</v>
       </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
@@ -5007,16 +4143,16 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -5030,49 +4166,7 @@
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI23" s="3" t="n">
+      <c r="AU23" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -5087,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5123,16 +4217,16 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
-        <v>-1</v>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -5188,11 +4282,15 @@
       <c r="AG24" t="n">
         <v>0</v>
       </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
@@ -5204,16 +4302,16 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -5227,49 +4325,7 @@
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI24" s="3" t="n">
+      <c r="AU24" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -5284,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5320,16 +4376,16 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="n">
-        <v>-1</v>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5385,11 +4441,15 @@
       <c r="AG25" t="n">
         <v>0</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
@@ -5401,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -5424,49 +4484,7 @@
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" s="3" t="n">
+      <c r="AU25" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -5491,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5517,16 +4535,16 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="n">
-        <v>-1</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5582,11 +4600,15 @@
       <c r="AG26" t="n">
         <v>0</v>
       </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -5598,16 +4620,16 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
@@ -5621,49 +4643,7 @@
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" s="3" t="n">
+      <c r="AU26" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -5678,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5714,16 +4694,16 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
-      <c r="M27" t="n">
-        <v>-1</v>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -5779,11 +4759,15 @@
       <c r="AG27" t="n">
         <v>0</v>
       </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -5795,16 +4779,16 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -5818,49 +4802,7 @@
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI27" s="3" t="n">
+      <c r="AU27" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -5875,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5911,16 +4853,16 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
-      <c r="M28" t="n">
-        <v>-1</v>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -5976,11 +4918,15 @@
       <c r="AG28" t="n">
         <v>0</v>
       </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -5992,16 +4938,16 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
@@ -6015,49 +4961,7 @@
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI28" s="3" t="n">
+      <c r="AU28" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -6072,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6108,16 +5012,16 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" t="n">
-        <v>-1</v>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6173,11 +5077,15 @@
       <c r="AG29" t="n">
         <v>0</v>
       </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -6189,16 +5097,16 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -6212,49 +5120,7 @@
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
+      <c r="AU29" s="3" t="n">
         <v>46171.58333333334</v>
       </c>
     </row>
@@ -6305,16 +5171,16 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
-        <v>-1</v>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -6370,11 +5236,15 @@
       <c r="AG30" t="n">
         <v>0</v>
       </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
@@ -6386,16 +5256,16 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -6409,49 +5279,7 @@
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
+      <c r="AU30" s="3" t="n">
         <v>46171.60416666666</v>
       </c>
     </row>
@@ -6502,16 +5330,16 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="n">
-        <v>-1</v>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6567,11 +5395,15 @@
       <c r="AG31" t="n">
         <v>0</v>
       </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
@@ -6583,16 +5415,16 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
@@ -6606,49 +5438,7 @@
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
+      <c r="AU31" s="3" t="n">
         <v>46171.60416666666</v>
       </c>
     </row>
@@ -6699,16 +5489,16 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>-1</v>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6764,11 +5554,15 @@
       <c r="AG32" t="n">
         <v>0</v>
       </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -6780,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
@@ -6803,49 +5597,7 @@
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
+      <c r="AU32" s="3" t="n">
         <v>46171.625</v>
       </c>
     </row>
@@ -6896,25 +5648,25 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>-1</v>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>1.65</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.88</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>4.93</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6941,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -6953,19 +5705,23 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
@@ -6977,16 +5733,16 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
@@ -7000,49 +5756,7 @@
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" s="3" t="n">
+      <c r="AU33" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -7057,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7093,19 +5807,19 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
-        <v>-1</v>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>1.65</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.94</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -7158,11 +5872,15 @@
       <c r="AG34" t="n">
         <v>0</v>
       </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -7174,16 +5892,16 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -7197,49 +5915,7 @@
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI34" s="3" t="n">
+      <c r="AU34" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -7254,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7290,25 +5966,25 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
-        <v>-1</v>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7355,11 +6031,15 @@
       <c r="AG35" t="n">
         <v>0</v>
       </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -7371,16 +6051,16 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ35" t="n">
         <v>0</v>
@@ -7394,49 +6074,7 @@
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI35" s="3" t="n">
+      <c r="AU35" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -7451,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7487,25 +6125,25 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" t="n">
-        <v>-1</v>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,19 +6182,23 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -7568,16 +6210,16 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ36" t="n">
         <v>0</v>
@@ -7591,49 +6233,7 @@
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" s="3" t="n">
+      <c r="AU36" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -7658,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7684,16 +6284,16 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
-        <v>-1</v>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7749,11 +6349,15 @@
       <c r="AG37" t="n">
         <v>0</v>
       </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -7765,16 +6369,16 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
@@ -7788,49 +6392,7 @@
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI37" s="3" t="n">
+      <c r="AU37" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -7855,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7881,16 +6443,16 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
-      <c r="M38" t="n">
-        <v>-1</v>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7946,11 +6508,15 @@
       <c r="AG38" t="n">
         <v>0</v>
       </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -7962,16 +6528,16 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -7985,49 +6551,7 @@
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="3" t="n">
+      <c r="AU38" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -8042,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8078,19 +6602,19 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
-      <c r="M39" t="n">
-        <v>-1</v>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>2.42</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.34</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -8123,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -8143,11 +6667,15 @@
       <c r="AG39" t="n">
         <v>0</v>
       </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -8159,16 +6687,16 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ39" t="n">
         <v>0</v>
@@ -8182,49 +6710,7 @@
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="3" t="n">
+      <c r="AU39" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -8239,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8275,19 +6761,19 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
-      <c r="M40" t="n">
-        <v>-1</v>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>4.37</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -8340,11 +6826,15 @@
       <c r="AG40" t="n">
         <v>0</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ40" t="n">
         <v>0</v>
@@ -8356,16 +6846,16 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
@@ -8379,49 +6869,7 @@
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="3" t="n">
+      <c r="AU40" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -8436,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8472,25 +6920,25 @@
       <c r="L41" t="n">
         <v>0</v>
       </c>
-      <c r="M41" t="n">
-        <v>-1</v>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N41" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8537,11 +6985,15 @@
       <c r="AG41" t="n">
         <v>0</v>
       </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
@@ -8553,16 +7005,16 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ41" t="n">
         <v>0</v>
@@ -8576,49 +7028,7 @@
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="3" t="n">
+      <c r="AU41" s="3" t="n">
         <v>46171.65625</v>
       </c>
     </row>
@@ -8669,16 +7079,16 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="n">
-        <v>-1</v>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -8734,11 +7144,15 @@
       <c r="AG42" t="n">
         <v>0</v>
       </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ42" t="n">
         <v>0</v>
@@ -8750,16 +7164,16 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
@@ -8773,49 +7187,7 @@
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="3" t="n">
+      <c r="AU42" s="3" t="n">
         <v>46171.66666666666</v>
       </c>
     </row>
@@ -8866,25 +7238,25 @@
       <c r="L43" t="n">
         <v>0</v>
       </c>
-      <c r="M43" t="n">
-        <v>-1</v>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>2.28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8931,11 +7303,15 @@
       <c r="AG43" t="n">
         <v>0</v>
       </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ43" t="n">
         <v>0</v>
@@ -8947,16 +7323,16 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
@@ -8970,49 +7346,7 @@
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="3" t="n">
+      <c r="AU43" s="3" t="n">
         <v>46171.66666666666</v>
       </c>
     </row>
@@ -9037,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9063,16 +7397,16 @@
       <c r="L44" t="n">
         <v>0</v>
       </c>
-      <c r="M44" t="n">
-        <v>-1</v>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -9128,11 +7462,15 @@
       <c r="AG44" t="n">
         <v>0</v>
       </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ44" t="n">
         <v>0</v>
@@ -9144,16 +7482,16 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ44" t="n">
         <v>0</v>
@@ -9167,49 +7505,7 @@
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="3" t="n">
+      <c r="AU44" s="3" t="n">
         <v>46171.67708333334</v>
       </c>
     </row>
@@ -9234,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9260,16 +7556,16 @@
       <c r="L45" t="n">
         <v>0</v>
       </c>
-      <c r="M45" t="n">
-        <v>-1</v>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N45" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -9325,11 +7621,15 @@
       <c r="AG45" t="n">
         <v>0</v>
       </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
@@ -9341,16 +7641,16 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ45" t="n">
         <v>0</v>
@@ -9364,49 +7664,7 @@
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI45" s="3" t="n">
+      <c r="AU45" s="3" t="n">
         <v>46171.67708333334</v>
       </c>
     </row>
@@ -9457,16 +7715,16 @@
       <c r="L46" t="n">
         <v>0</v>
       </c>
-      <c r="M46" t="n">
-        <v>-1</v>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -9522,11 +7780,15 @@
       <c r="AG46" t="n">
         <v>0</v>
       </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ46" t="n">
         <v>0</v>
@@ -9538,16 +7800,16 @@
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
@@ -9561,49 +7823,7 @@
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="3" t="n">
+      <c r="AU46" s="3" t="n">
         <v>46171.79166666666</v>
       </c>
     </row>
@@ -9654,16 +7874,16 @@
       <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="n">
-        <v>-1</v>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -9719,11 +7939,15 @@
       <c r="AG47" t="n">
         <v>0</v>
       </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ47" t="n">
         <v>0</v>
@@ -9735,16 +7959,16 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ47" t="n">
         <v>0</v>
@@ -9758,49 +7982,7 @@
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI47" s="3" t="n">
+      <c r="AU47" s="3" t="n">
         <v>46171.83333333334</v>
       </c>
     </row>
@@ -9815,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9851,16 +8033,16 @@
       <c r="L48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="n">
-        <v>-1</v>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -9916,11 +8098,15 @@
       <c r="AG48" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ48" t="n">
         <v>0</v>
@@ -9932,16 +8118,16 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ48" t="n">
         <v>0</v>
@@ -9955,49 +8141,7 @@
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="3" t="n">
+      <c r="AU48" s="3" t="n">
         <v>46171.83333333334</v>
       </c>
     </row>
@@ -10012,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10048,16 +8192,16 @@
       <c r="L49" t="n">
         <v>0</v>
       </c>
-      <c r="M49" t="n">
-        <v>-1</v>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -10113,11 +8257,15 @@
       <c r="AG49" t="n">
         <v>0</v>
       </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
@@ -10129,16 +8277,16 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ49" t="n">
         <v>0</v>
@@ -10152,49 +8300,7 @@
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI49" s="3" t="n">
+      <c r="AU49" s="3" t="n">
         <v>46171.83333333334</v>
       </c>
     </row>
@@ -10209,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10245,16 +8351,16 @@
       <c r="L50" t="n">
         <v>0</v>
       </c>
-      <c r="M50" t="n">
-        <v>-1</v>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -10310,11 +8416,15 @@
       <c r="AG50" t="n">
         <v>0</v>
       </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
@@ -10326,16 +8436,16 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ50" t="n">
         <v>0</v>
@@ -10349,49 +8459,7 @@
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI50" s="3" t="n">
+      <c r="AU50" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -10416,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10442,16 +8510,16 @@
       <c r="L51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="n">
-        <v>-1</v>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -10507,11 +8575,15 @@
       <c r="AG51" t="n">
         <v>0</v>
       </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ51" t="n">
         <v>0</v>
@@ -10523,16 +8595,16 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ51" t="n">
         <v>0</v>
@@ -10546,49 +8618,7 @@
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" s="3" t="n">
+      <c r="AU51" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -10603,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10639,16 +8669,16 @@
       <c r="L52" t="n">
         <v>0</v>
       </c>
-      <c r="M52" t="n">
-        <v>-1</v>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -10704,11 +8734,15 @@
       <c r="AG52" t="n">
         <v>0</v>
       </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ52" t="n">
         <v>0</v>
@@ -10720,16 +8754,16 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ52" t="n">
         <v>0</v>
@@ -10743,49 +8777,7 @@
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI52" s="3" t="n">
+      <c r="AU52" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -10810,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10836,16 +8828,16 @@
       <c r="L53" t="n">
         <v>0</v>
       </c>
-      <c r="M53" t="n">
-        <v>-1</v>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -10901,11 +8893,15 @@
       <c r="AG53" t="n">
         <v>0</v>
       </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ53" t="n">
         <v>0</v>
@@ -10917,16 +8913,16 @@
         <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ53" t="n">
         <v>0</v>
@@ -10940,49 +8936,7 @@
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI53" s="3" t="n">
+      <c r="AU53" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -10997,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11033,16 +8987,16 @@
       <c r="L54" t="n">
         <v>0</v>
       </c>
-      <c r="M54" t="n">
-        <v>-1</v>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N54" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -11098,11 +9052,15 @@
       <c r="AG54" t="n">
         <v>0</v>
       </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ54" t="n">
         <v>0</v>
@@ -11114,16 +9072,16 @@
         <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ54" t="n">
         <v>0</v>
@@ -11137,49 +9095,7 @@
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="3" t="n">
+      <c r="AU54" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -11204,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11230,16 +9146,16 @@
       <c r="L55" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="n">
-        <v>-1</v>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -11295,11 +9211,15 @@
       <c r="AG55" t="n">
         <v>0</v>
       </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ55" t="n">
         <v>0</v>
@@ -11311,16 +9231,16 @@
         <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ55" t="n">
         <v>0</v>
@@ -11334,49 +9254,7 @@
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="3" t="n">
+      <c r="AU55" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -11427,16 +9305,16 @@
       <c r="L56" t="n">
         <v>0</v>
       </c>
-      <c r="M56" t="n">
-        <v>-1</v>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -11492,11 +9370,15 @@
       <c r="AG56" t="n">
         <v>0</v>
       </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ56" t="n">
         <v>0</v>
@@ -11508,16 +9390,16 @@
         <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ56" t="n">
         <v>0</v>
@@ -11531,49 +9413,7 @@
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="3" t="n">
+      <c r="AU56" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -11588,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11624,16 +9464,16 @@
       <c r="L57" t="n">
         <v>0</v>
       </c>
-      <c r="M57" t="n">
-        <v>-1</v>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -11689,11 +9529,15 @@
       <c r="AG57" t="n">
         <v>0</v>
       </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ57" t="n">
         <v>0</v>
@@ -11705,16 +9549,16 @@
         <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ57" t="n">
         <v>0</v>
@@ -11728,49 +9572,7 @@
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="3" t="n">
+      <c r="AU57" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -11785,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11821,16 +9623,16 @@
       <c r="L58" t="n">
         <v>0</v>
       </c>
-      <c r="M58" t="n">
-        <v>-1</v>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N58" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -11886,11 +9688,15 @@
       <c r="AG58" t="n">
         <v>0</v>
       </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>0</v>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ58" t="n">
         <v>0</v>
@@ -11902,16 +9708,16 @@
         <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ58" t="n">
         <v>0</v>
@@ -11925,49 +9731,7 @@
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI58" s="3" t="n">
+      <c r="AU58" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -11982,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12018,16 +9782,16 @@
       <c r="L59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="n">
-        <v>-1</v>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N59" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -12083,11 +9847,15 @@
       <c r="AG59" t="n">
         <v>0</v>
       </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ59" t="n">
         <v>0</v>
@@ -12099,16 +9867,16 @@
         <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ59" t="n">
         <v>0</v>
@@ -12122,49 +9890,7 @@
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI59" s="3" t="n">
+      <c r="AU59" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -12179,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12215,16 +9941,16 @@
       <c r="L60" t="n">
         <v>0</v>
       </c>
-      <c r="M60" t="n">
-        <v>-1</v>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -12280,11 +10006,15 @@
       <c r="AG60" t="n">
         <v>0</v>
       </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ60" t="n">
         <v>0</v>
@@ -12296,16 +10026,16 @@
         <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ60" t="n">
         <v>0</v>
@@ -12319,49 +10049,7 @@
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI60" s="3" t="n">
+      <c r="AU60" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -12376,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12412,16 +10100,16 @@
       <c r="L61" t="n">
         <v>0</v>
       </c>
-      <c r="M61" t="n">
-        <v>-1</v>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N61" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -12477,11 +10165,15 @@
       <c r="AG61" t="n">
         <v>0</v>
       </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ61" t="n">
         <v>0</v>
@@ -12493,16 +10185,16 @@
         <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ61" t="n">
         <v>0</v>
@@ -12516,49 +10208,7 @@
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI61" s="3" t="n">
+      <c r="AU61" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -12573,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12609,16 +10259,16 @@
       <c r="L62" t="n">
         <v>0</v>
       </c>
-      <c r="M62" t="n">
-        <v>-1</v>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -12674,11 +10324,15 @@
       <c r="AG62" t="n">
         <v>0</v>
       </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ62" t="n">
         <v>0</v>
@@ -12690,16 +10344,16 @@
         <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ62" t="n">
         <v>0</v>
@@ -12713,49 +10367,7 @@
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI62" s="3" t="n">
+      <c r="AU62" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -12780,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12806,16 +10418,16 @@
       <c r="L63" t="n">
         <v>0</v>
       </c>
-      <c r="M63" t="n">
-        <v>-1</v>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -12871,11 +10483,15 @@
       <c r="AG63" t="n">
         <v>0</v>
       </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ63" t="n">
         <v>0</v>
@@ -12887,16 +10503,16 @@
         <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP63" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ63" t="n">
         <v>0</v>
@@ -12910,49 +10526,7 @@
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI63" s="3" t="n">
+      <c r="AU63" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -12967,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13003,16 +10577,16 @@
       <c r="L64" t="n">
         <v>0</v>
       </c>
-      <c r="M64" t="n">
-        <v>-1</v>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -13068,11 +10642,15 @@
       <c r="AG64" t="n">
         <v>0</v>
       </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ64" t="n">
         <v>0</v>
@@ -13084,16 +10662,16 @@
         <v>0</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ64" t="n">
         <v>0</v>
@@ -13107,49 +10685,7 @@
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI64" s="3" t="n">
+      <c r="AU64" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -13200,16 +10736,16 @@
       <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="n">
-        <v>-1</v>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -13265,11 +10801,15 @@
       <c r="AG65" t="n">
         <v>0</v>
       </c>
-      <c r="AH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>0</v>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ65" t="n">
         <v>0</v>
@@ -13281,16 +10821,16 @@
         <v>0</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ65" t="n">
         <v>0</v>
@@ -13304,49 +10844,7 @@
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI65" s="3" t="n">
+      <c r="AU65" s="3" t="n">
         <v>46171.875</v>
       </c>
     </row>
@@ -13397,16 +10895,16 @@
       <c r="L66" t="n">
         <v>0</v>
       </c>
-      <c r="M66" t="n">
-        <v>-1</v>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
@@ -13462,11 +10960,15 @@
       <c r="AG66" t="n">
         <v>0</v>
       </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ66" t="n">
         <v>0</v>
@@ -13478,16 +10980,16 @@
         <v>0</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP66" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ66" t="n">
         <v>0</v>
@@ -13501,49 +11003,7 @@
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="3" t="n">
+      <c r="AU66" s="3" t="n">
         <v>46171.89583333334</v>
       </c>
     </row>
@@ -13594,16 +11054,16 @@
       <c r="L67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
-        <v>-1</v>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -13659,11 +11119,15 @@
       <c r="AG67" t="n">
         <v>0</v>
       </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>0</v>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ67" t="n">
         <v>0</v>
@@ -13675,16 +11139,16 @@
         <v>0</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ67" t="n">
         <v>0</v>
@@ -13698,49 +11162,7 @@
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="3" t="n">
+      <c r="AU67" s="3" t="n">
         <v>46171.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5657,10 +5657,10 @@
         <v>1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P33" t="n">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P34" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O33" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="P33" t="n">
-        <v>4.93</v>
+        <v>3.63</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.37</v>
+        <v>1.93</v>
       </c>
       <c r="O37" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="P40" t="n">
-        <v>2.78</v>
+        <v>4.93</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P33" t="n">
-        <v>3.63</v>
+        <v>4.84</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="O37" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="O33" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P33" t="n">
-        <v>4.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>4.84</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>4.93</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="P39" t="n">
-        <v>4.93</v>
+        <v>3.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P44" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>5.22</v>
       </c>
       <c r="O24" t="n">
-        <v>3.83</v>
+        <v>4.61</v>
       </c>
       <c r="P24" t="n">
-        <v>3.91</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,49 +5654,49 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>4.37</v>
+        <v>1.73</v>
       </c>
       <c r="O33" t="n">
         <v>3.54</v>
       </c>
       <c r="P33" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>4.22</v>
+        <v>4.93</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P38" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P39" t="n">
-        <v>3.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O44" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P44" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="O25" t="n">
         <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="O28" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="P28" t="n">
-        <v>3.91</v>
+        <v>2.98</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="P29" t="n">
-        <v>2.98</v>
+        <v>3.91</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46171.60416666666</v>
+        <v>46171.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -5448,27 +5448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46171.625</v>
+        <v>46171.60416666666</v>
       </c>
     </row>
     <row r="33">
@@ -5607,27 +5607,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46171.65625</v>
+        <v>46171.625</v>
       </c>
     </row>
     <row r="34">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="P35" t="n">
-        <v>4.93</v>
+        <v>3.63</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="P38" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>4.84</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>1.93</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="AU42" s="3" t="n">
-        <v>46171.66666666666</v>
+        <v>46171.65625</v>
       </c>
     </row>
     <row r="43">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>4.17</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7448,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46171.67708333334</v>
+        <v>46171.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46171.79166666666</v>
+        <v>46171.67708333334</v>
       </c>
     </row>
     <row r="47">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46171.83333333334</v>
+        <v>46171.79166666666</v>
       </c>
     </row>
     <row r="48">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46171.875</v>
+        <v>46171.83333333334</v>
       </c>
     </row>
     <row r="51">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10854,27 +10854,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46171.89583333334</v>
+        <v>46171.875</v>
       </c>
     </row>
     <row r="67">
@@ -11013,156 +11013,315 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="3" t="n">
+        <v>46171.89583333334</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Sporting KC II</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="3" t="n">
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
         <v>46171.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
         <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="O26" t="n">
         <v>4.61</v>
       </c>
       <c r="P26" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4.37</v>
+        <v>1.93</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>3.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6611,10 +6611,10 @@
         <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>3.48</v>
+        <v>3.94</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>4.84</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O35" t="n">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.78</v>
+        <v>4.93</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P39" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
         <v>4.61</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P34" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>4.93</v>
+        <v>2.78</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>3.4</v>
+        <v>4.93</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>4.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.89</v>
+        <v>5.22</v>
       </c>
       <c r="O23" t="n">
-        <v>3.83</v>
+        <v>4.61</v>
       </c>
       <c r="P23" t="n">
-        <v>3.91</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.71</v>
+        <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>2.26</v>
       </c>
       <c r="O26" t="n">
-        <v>4.61</v>
+        <v>3.71</v>
       </c>
       <c r="P26" t="n">
-        <v>5.22</v>
+        <v>2.98</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.93</v>
+        <v>4.37</v>
       </c>
       <c r="O34" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P35" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>4.84</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>4.22</v>
+        <v>4.93</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O42" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P42" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5.22</v>
+        <v>1.89</v>
       </c>
       <c r="O23" t="n">
-        <v>4.61</v>
+        <v>3.83</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>3.91</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P38" t="n">
-        <v>4.22</v>
+        <v>3.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>4.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>4.84</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4.61</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>5.22</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>4.61</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>5.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P35" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>4.93</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>4.37</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="P41" t="n">
-        <v>4.93</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="P28" t="n">
-        <v>2.98</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="O29" t="n">
         <v>4.61</v>
       </c>
       <c r="P29" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O38" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P38" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>4.84</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O40" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="P40" t="n">
-        <v>4.93</v>
+        <v>3.63</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>1.8</v>
+        <v>4.93</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O42" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P42" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="O23" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>3.83</v>
       </c>
       <c r="P24" t="n">
-        <v>4.19</v>
+        <v>3.91</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.83</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>3.91</v>
+        <v>4.19</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>5.22</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>4.61</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P34" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.48</v>
+        <v>3.94</v>
       </c>
       <c r="P38" t="n">
-        <v>3.4</v>
+        <v>4.84</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P39" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,22 +10223,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>4.61</v>
+        <v>2.99</v>
       </c>
       <c r="P21" t="n">
-        <v>5.22</v>
+        <v>4.19</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.26</v>
+        <v>5.22</v>
       </c>
       <c r="O23" t="n">
-        <v>3.71</v>
+        <v>4.61</v>
       </c>
       <c r="P23" t="n">
-        <v>2.98</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O24" t="n">
-        <v>3.83</v>
+        <v>4.61</v>
       </c>
       <c r="P24" t="n">
-        <v>3.91</v>
+        <v>5.22</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>3.34</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.22</v>
+        <v>2.26</v>
       </c>
       <c r="O30" t="n">
-        <v>4.61</v>
+        <v>3.71</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="P37" t="n">
-        <v>4.93</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6452,10 +6452,10 @@
         <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P38" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P40" t="n">
-        <v>4.22</v>
+        <v>4.84</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="O20" t="n">
-        <v>2.66</v>
+        <v>4.61</v>
       </c>
       <c r="P20" t="n">
-        <v>3.17</v>
+        <v>5.22</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>2.99</v>
+        <v>3.71</v>
       </c>
       <c r="P21" t="n">
-        <v>4.19</v>
+        <v>2.98</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O26" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="P26" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O30" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P35" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P40" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O42" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P42" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.22</v>
+        <v>2.26</v>
       </c>
       <c r="O17" t="n">
-        <v>4.61</v>
+        <v>3.71</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>2.98</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O21" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="P21" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>4.19</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="P30" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>2.78</v>
+        <v>4.22</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P41" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P42" t="n">
-        <v>3.63</v>
+        <v>4.84</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="P21" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>5.22</v>
+        <v>2.31</v>
       </c>
       <c r="O24" t="n">
-        <v>4.61</v>
+        <v>2.72</v>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>3.34</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>4.19</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>5.22</v>
       </c>
       <c r="O30" t="n">
-        <v>2.66</v>
+        <v>4.61</v>
       </c>
       <c r="P30" t="n">
-        <v>3.17</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.93</v>
+        <v>4.37</v>
       </c>
       <c r="O35" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>4.37</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>4.93</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="O39" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P39" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O42" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P42" t="n">
-        <v>4.84</v>
+        <v>3.63</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.83</v>
+        <v>2.66</v>
       </c>
       <c r="P16" t="n">
-        <v>3.91</v>
+        <v>3.17</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>3.34</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>3.34</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>4.37</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6293,10 +6293,10 @@
         <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P37" t="n">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
         <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>4.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P42" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O18" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="P18" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="P20" t="n">
-        <v>3.34</v>
+        <v>4.19</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>4.61</v>
       </c>
       <c r="P22" t="n">
-        <v>4.19</v>
+        <v>5.22</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="O26" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="P26" t="n">
-        <v>3.91</v>
+        <v>2.98</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>4.61</v>
+        <v>3.83</v>
       </c>
       <c r="P27" t="n">
-        <v>5.22</v>
+        <v>3.91</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O28" t="n">
         <v>3.9</v>
       </c>
-      <c r="O28" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P28" t="n">
-        <v>1.85</v>
+        <v>5.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.22</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O37" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P37" t="n">
-        <v>4.84</v>
+        <v>3.63</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>4.93</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.93</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="P41" t="n">
-        <v>4.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="O42" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>4.22</v>
+        <v>3.29</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="P18" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>7.41</v>
       </c>
       <c r="O19" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>3.17</v>
+        <v>1.38</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="O22" t="n">
         <v>4.61</v>
       </c>
       <c r="P22" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>9.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5.22</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
         <v>4.61</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>5.22</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.26</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.98</v>
+        <v>5.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>3.91</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="P28" t="n">
-        <v>5.95</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O32" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P32" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="O34" t="n">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="P34" t="n">
-        <v>4.84</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>1.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="P35" t="n">
-        <v>2.78</v>
+        <v>4.22</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>8.199999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O37" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="P37" t="n">
-        <v>3.63</v>
+        <v>4.93</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="O38" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P38" t="n">
-        <v>4.93</v>
+        <v>3.29</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>4.22</v>
+        <v>4.84</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="P41" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.07</v>
+        <v>1.32</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="P42" t="n">
-        <v>3.29</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O45" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O46" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>5.02</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>9.449999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>5.95</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.45</v>
+        <v>5.22</v>
       </c>
       <c r="O18" t="n">
-        <v>2.66</v>
+        <v>4.61</v>
       </c>
       <c r="P18" t="n">
-        <v>3.17</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>7.41</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P25" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
-        <v>5.95</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>3.17</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O29" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="P29" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="O34" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O35" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P35" t="n">
-        <v>4.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="O37" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="P37" t="n">
-        <v>4.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.07</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>3.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>1.65</v>
       </c>
       <c r="O41" t="n">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>4.93</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="P42" t="n">
-        <v>8.199999999999999</v>
+        <v>4.84</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8474,22 +8474,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU68"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>2.31</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>5.95</v>
+        <v>3.34</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>7.41</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="P25" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>5.22</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>4.61</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>7.41</v>
       </c>
       <c r="O27" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="P27" t="n">
-        <v>3.17</v>
+        <v>1.38</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="P29" t="n">
-        <v>3.34</v>
+        <v>5.95</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3.71</v>
+        <v>2.99</v>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>4.19</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46171.625</v>
+        <v>46171.60416666666</v>
       </c>
     </row>
     <row r="34">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P34" t="n">
-        <v>3.29</v>
+        <v>4.82</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46171.65625</v>
+        <v>46171.625</v>
       </c>
     </row>
     <row r="35">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.93</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>4.84</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>1.88</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>3.63</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>4.37</v>
       </c>
       <c r="O39" t="n">
         <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>4.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="O40" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="P40" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O42" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P42" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46171.66666666666</v>
+        <v>46171.65625</v>
       </c>
     </row>
     <row r="44">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46171.67708333334</v>
+        <v>46171.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46171.79166666666</v>
+        <v>46171.67708333334</v>
       </c>
     </row>
     <row r="48">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46171.83333333334</v>
+        <v>46171.79166666666</v>
       </c>
     </row>
     <row r="49">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46171.875</v>
+        <v>46171.83333333334</v>
       </c>
     </row>
     <row r="52">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.66</v>
+        <v>2.51</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="P53" t="n">
-        <v>5.35</v>
+        <v>2.99</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11013,27 +11013,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46171.89583333334</v>
+        <v>46171.875</v>
       </c>
     </row>
     <row r="68">
@@ -11172,156 +11172,315 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
+        <v>46171.89583333334</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Sporting KC II</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" s="3" t="n">
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="3" t="n">
         <v>46171.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>5.02</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.02</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="O17" t="n">
-        <v>2.72</v>
+        <v>3.71</v>
       </c>
       <c r="P17" t="n">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>9.449999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="O19" t="n">
-        <v>4.9</v>
+        <v>3.83</v>
       </c>
       <c r="P19" t="n">
-        <v>1.28</v>
+        <v>3.91</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.91</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>5.22</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>4.61</v>
       </c>
       <c r="P23" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="O25" t="n">
-        <v>3.71</v>
+        <v>2.72</v>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5.22</v>
+        <v>1.9</v>
       </c>
       <c r="O26" t="n">
-        <v>4.61</v>
+        <v>2.99</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>4.19</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>7.41</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.38</v>
+        <v>5.95</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P28" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="P29" t="n">
-        <v>5.95</v>
+        <v>3.17</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>7.41</v>
       </c>
       <c r="O30" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>4.19</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>2.07</v>
       </c>
       <c r="O35" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.78</v>
+        <v>3.29</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>4.84</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.32</v>
+        <v>1.93</v>
       </c>
       <c r="O37" t="n">
-        <v>4.7</v>
+        <v>3.48</v>
       </c>
       <c r="P37" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O38" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>3.63</v>
+        <v>4.22</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.37</v>
+        <v>1.65</v>
       </c>
       <c r="O39" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>1.8</v>
+        <v>4.84</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="O40" t="n">
-        <v>3.48</v>
+        <v>4.7</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="P41" t="n">
-        <v>4.93</v>
+        <v>2.78</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="P42" t="n">
-        <v>4.22</v>
+        <v>4.93</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.07</v>
+        <v>4.37</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P43" t="n">
-        <v>3.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.51</v>
+        <v>2.93</v>
       </c>
       <c r="O53" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="P53" t="n">
-        <v>2.99</v>
+        <v>2.22</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,16 +8867,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.02</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>9.449999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="O18" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>3.83</v>
+        <v>4.61</v>
       </c>
       <c r="P19" t="n">
-        <v>3.91</v>
+        <v>5.22</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>2.72</v>
+        <v>4.9</v>
       </c>
       <c r="P25" t="n">
-        <v>3.34</v>
+        <v>1.28</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="O27" t="n">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="P27" t="n">
-        <v>5.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="P28" t="n">
-        <v>1.85</v>
+        <v>3.91</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O29" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="P29" t="n">
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.41</v>
+        <v>5.22</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>4.61</v>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P31" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P32" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>3.29</v>
+        <v>4.93</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="P38" t="n">
-        <v>4.22</v>
+        <v>4.84</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O39" t="n">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>4.84</v>
+        <v>4.22</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.32</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>4.7</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>1.32</v>
       </c>
       <c r="O41" t="n">
-        <v>3.34</v>
+        <v>4.7</v>
       </c>
       <c r="P41" t="n">
-        <v>2.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="O42" t="n">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>4.93</v>
+        <v>3.29</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4.37</v>
+        <v>1.88</v>
       </c>
       <c r="O43" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="P43" t="n">
-        <v>1.8</v>
+        <v>3.63</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.93</v>
+        <v>1.89</v>
       </c>
       <c r="O53" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="P53" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.51</v>
+        <v>1.66</v>
       </c>
       <c r="O66" t="n">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="P66" t="n">
-        <v>2.99</v>
+        <v>5.35</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1529,55 +1529,55 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>5.02</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O16" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="P16" t="n">
-        <v>3.17</v>
+        <v>3.34</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>7.41</v>
+        <v>5.22</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>4.61</v>
       </c>
       <c r="P18" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>4.61</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>5.22</v>
+        <v>1.85</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>4.66</v>
       </c>
       <c r="P21" t="n">
-        <v>5.95</v>
+        <v>5.16</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>3.91</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.31</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>2.72</v>
+        <v>3.83</v>
       </c>
       <c r="P29" t="n">
-        <v>3.34</v>
+        <v>3.91</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>5.22</v>
+        <v>7.41</v>
       </c>
       <c r="O30" t="n">
-        <v>4.61</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5975,10 +5975,10 @@
         <v>1.65</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="P35" t="n">
-        <v>4.93</v>
+        <v>4.84</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P36" t="n">
-        <v>2.78</v>
+        <v>3.63</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="O37" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P38" t="n">
-        <v>4.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.73</v>
+        <v>4.37</v>
       </c>
       <c r="O39" t="n">
         <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>4.22</v>
+        <v>1.8</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>1.93</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.32</v>
+        <v>2.07</v>
       </c>
       <c r="O41" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>8.199999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="P42" t="n">
-        <v>3.29</v>
+        <v>4.93</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="O43" t="n">
-        <v>3.42</v>
+        <v>4.7</v>
       </c>
       <c r="P43" t="n">
-        <v>3.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11093,10 +11093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.02</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>3.34</v>
+        <v>5.95</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.22</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.61</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.62</v>
       </c>
       <c r="P19" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>4.66</v>
+        <v>3.56</v>
       </c>
       <c r="P21" t="n">
-        <v>5.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>4.61</v>
+        <v>2.72</v>
       </c>
       <c r="P23" t="n">
-        <v>5.22</v>
+        <v>3.34</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4232,55 +4232,55 @@
         <v>4.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>9.449999999999999</v>
+        <v>2.45</v>
       </c>
       <c r="O25" t="n">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>3.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>7.41</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="P26" t="n">
-        <v>5.95</v>
+        <v>1.38</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.26</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>3.71</v>
+        <v>4.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.98</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>4.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>5.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="O29" t="n">
-        <v>3.83</v>
+        <v>2.98</v>
       </c>
       <c r="P29" t="n">
-        <v>3.91</v>
+        <v>3.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.41</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O31" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O33" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P33" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O34" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P34" t="n">
-        <v>4.82</v>
+        <v>4.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="O35" t="n">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>4.84</v>
+        <v>3.02</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P36" t="n">
-        <v>3.63</v>
+        <v>2.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O37" t="n">
         <v>3.54</v>
       </c>
       <c r="P37" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,25 +6608,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4.37</v>
+        <v>2.07</v>
       </c>
       <c r="O39" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>1.8</v>
+        <v>3.29</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6641,31 +6641,31 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.93</v>
+        <v>4.37</v>
       </c>
       <c r="O40" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P41" t="n">
-        <v>3.29</v>
+        <v>5.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>4.93</v>
+        <v>2.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7253,10 +7253,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -7265,10 +7265,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -7277,31 +7277,31 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="O44" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U44" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.17</v>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="O47" t="n">
-        <v>4.17</v>
+        <v>3.8</v>
       </c>
       <c r="P47" t="n">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7925,10 +7925,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,22 +10700,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>5.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>4.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="T18" t="n">
-        <v>3.42</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>4.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,65 +3428,65 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>2.31</v>
       </c>
       <c r="O19" t="n">
-        <v>4.62</v>
+        <v>2.72</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.91</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.5</v>
-      </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>2.14</v>
+        <v>3.58</v>
       </c>
       <c r="V19" t="n">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.3</v>
+        <v>2.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.41</v>
+        <v>2.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>5.46</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>5.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
-        <v>3.56</v>
+        <v>2.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>3.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="S21" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>2.62</v>
+        <v>3.98</v>
       </c>
       <c r="V21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.43</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>3.9</v>
       </c>
       <c r="O23" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>3.34</v>
+        <v>1.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>4.19</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.49</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.41</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.53</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>7.41</v>
+        <v>4.8</v>
       </c>
       <c r="O26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>9.449999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="O27" t="n">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>5.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="O28" t="n">
-        <v>4.66</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>5.16</v>
+        <v>3.65</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.91</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG28" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.04</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>2.98</v>
+        <v>4.9</v>
       </c>
       <c r="P29" t="n">
-        <v>3.65</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>7.41</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5504,10 +5504,10 @@
         <v>3.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5528,31 +5528,31 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5660,13 +5660,13 @@
         <v>3.35</v>
       </c>
       <c r="P33" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5687,31 +5687,31 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P35" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S36" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T36" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="U36" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
         <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="O37" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="P37" t="n">
-        <v>4.26</v>
+        <v>3.29</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T37" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O38" t="n">
         <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6</v>
+        <v>5.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.3</v>
       </c>
-      <c r="T38" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,25 +6608,25 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P39" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6641,31 +6641,31 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,61 +6926,61 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="O41" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P41" t="n">
-        <v>5.07</v>
+        <v>4.26</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R41" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T41" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="U41" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="V41" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA41" t="n">
         <v>1.85</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
         <v>1.91</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.3</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>3.38</v>
-      </c>
       <c r="AD42" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG42" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8207,55 +8207,55 @@
         <v>3.74</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="O61" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="P61" t="n">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,16 +10139,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>5.02</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.02</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>3.7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>4.66</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>5.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="O17" t="n">
-        <v>4.04</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>4.12</v>
+        <v>3.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>2.33</v>
+        <v>3.27</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.99</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>4.19</v>
+        <v>5.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.31</v>
+        <v>7.41</v>
       </c>
       <c r="O19" t="n">
-        <v>2.72</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>3.34</v>
+        <v>1.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.46</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="P20" t="n">
-        <v>5.95</v>
+        <v>3.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="O21" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="P21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Q21" t="n">
         <v>3.17</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.44</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="S21" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="U21" t="n">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.6</v>
+        <v>5.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
         <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O23" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.6</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,80 +4541,80 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>4.4</v>
+        <v>3.56</v>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T26" t="n">
-        <v>3.88</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="V26" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
-        <v>4.66</v>
+        <v>2.99</v>
       </c>
       <c r="P27" t="n">
-        <v>5.16</v>
+        <v>4.19</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="S27" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.15</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.05</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AG27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.65</v>
+        <v>1.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.19</v>
+        <v>1.75</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.63</v>
+        <v>1.15</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>9.449999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -5357,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5369,31 +5369,31 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,19 +5495,19 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5528,31 +5528,31 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O35" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P35" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.3</v>
       </c>
-      <c r="O36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R36" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U36" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="V36" t="n">
         <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
         <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.6</v>
+        <v>4.37</v>
       </c>
       <c r="O38" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>5.07</v>
+        <v>1.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="O39" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="P39" t="n">
-        <v>3.02</v>
+        <v>5.07</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.37</v>
+        <v>1.75</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P41" t="n">
-        <v>4.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S41" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T41" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="U41" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="V41" t="n">
         <v>1.36</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q42" t="n">
         <v>1.75</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R42" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="S42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V42" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA42" t="n">
         <v>1.67</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="n">
         <v>2.7</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S43" t="n">
         <v>1.32</v>
       </c>
-      <c r="O43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P43" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U43" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="V43" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AB43" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.66</v>
+        <v>2.17</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9905,22 +9905,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,22 +10064,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1529,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
         <v>1.26</v>
@@ -1562,13 +1562,13 @@
         <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
         <v>1.15</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5.02</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2798,58 +2798,58 @@
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="O16" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>5.16</v>
+        <v>7.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.5625</v>
       </c>
     </row>
     <row r="17">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.04</v>
+        <v>4.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>4.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.36</v>
+        <v>3.85</v>
       </c>
       <c r="U17" t="n">
-        <v>3.27</v>
+        <v>2.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.29</v>
+        <v>1.71</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>2.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.78</v>
+        <v>2.55</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.63</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3272,61 +3272,61 @@
         <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>4.62</v>
       </c>
       <c r="P18" t="n">
-        <v>5.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7.41</v>
+        <v>3.86</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>3.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.04</v>
+        <v>2.89</v>
       </c>
       <c r="U20" t="n">
-        <v>3.98</v>
+        <v>2.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.43</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,22 +3704,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.17</v>
+        <v>2.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>2.11</v>
+        <v>3.42</v>
       </c>
       <c r="U21" t="n">
-        <v>3.58</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="W21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.01</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.33</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.12</v>
+        <v>1.49</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,31 +3905,31 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O22" t="n">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>5.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>2.5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U22" t="n">
         <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
         <v>1.15</v>
@@ -3938,31 +3938,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="n">
         <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.74</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>4.04</v>
+        <v>4.9</v>
       </c>
       <c r="P23" t="n">
-        <v>4.12</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>4.19</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.52</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.38</v>
+        <v>4.53</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4415,31 +4415,31 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>3.56</v>
+        <v>2.72</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>3.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S26" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>2.11</v>
       </c>
       <c r="U26" t="n">
-        <v>2.62</v>
+        <v>3.58</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.81</v>
+        <v>2.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>3</v>
+        <v>5.46</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="O27" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="P27" t="n">
-        <v>4.19</v>
+        <v>3.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T27" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="V27" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.53</v>
+        <v>3.82</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.9</v>
+        <v>7.41</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>1.38</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>9.449999999999999</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>3.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>3.09</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="R31" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
         <v>2.32</v>
       </c>
       <c r="V31" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46171.60416666666</v>
+        <v>46171.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -5766,27 +5766,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P34" t="n">
-        <v>4.45</v>
+        <v>3.09</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="V34" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46171.625</v>
+        <v>46171.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -5925,27 +5925,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="O35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T35" t="n">
         <v>3.34</v>
       </c>
-      <c r="P35" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46171.65625</v>
+        <v>46171.625</v>
       </c>
     </row>
     <row r="36">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,80 +6131,80 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P36" t="n">
-        <v>4.26</v>
+        <v>2.85</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y36" t="n">
         <v>1.36</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="Z36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.36</v>
       </c>
-      <c r="W36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="O37" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P37" t="n">
-        <v>3.29</v>
+        <v>2.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R37" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S37" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>4.37</v>
+        <v>1.27</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="P38" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="O39" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P39" t="n">
-        <v>5.07</v>
+        <v>3.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AC39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6803,7 +6803,7 @@
         <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
         <v>1.67</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="P41" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD42" t="n">
         <v>1.32</v>
       </c>
-      <c r="O42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="P42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE42" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,65 +7244,65 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R43" t="n">
         <v>2.2</v>
       </c>
-      <c r="O43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S43" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T43" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U43" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="V43" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W43" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
         <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AB43" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46171.66666666666</v>
+        <v>46171.65625</v>
       </c>
     </row>
     <row r="45">
@@ -7571,13 +7571,13 @@
         <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S45" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T45" t="n">
         <v>2.53</v>
@@ -7592,28 +7592,28 @@
         <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
         <v>2.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AB45" t="n">
         <v>1.62</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD45" t="n">
         <v>1.2</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF45" t="n">
         <v>1.85</v>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7766,10 +7766,10 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46171.67708333334</v>
+        <v>46171.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="O47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P47" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="O48" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="R48" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AA48" t="n">
         <v>1.35</v>
       </c>
-      <c r="T48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB48" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.05</v>
+        <v>3.14</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46171.79166666666</v>
+        <v>46171.67708333334</v>
       </c>
     </row>
     <row r="49">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46171.83333333334</v>
+        <v>46171.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8525,10 +8525,10 @@
         <v>3.74</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R51" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S51" t="n">
         <v>1.33</v>
@@ -8537,13 +8537,13 @@
         <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V51" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W51" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
         <v>1.01</v>
@@ -8555,7 +8555,7 @@
         <v>3.42</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AB51" t="n">
         <v>1.87</v>
@@ -8573,7 +8573,7 @@
         <v>1.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46171.875</v>
+        <v>46171.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,22 +9587,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,64 +10583,64 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10859,22 +10859,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11018,22 +11018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11172,27 +11172,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="3" t="n">
-        <v>46171.89583333334</v>
+        <v>46171.875</v>
       </c>
     </row>
     <row r="69">
@@ -11331,156 +11331,315 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="3" t="n">
+        <v>46171.89583333334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Sporting KC II</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU69" s="3" t="n">
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="3" t="n">
         <v>46171.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU70"/>
+  <dimension ref="A1:AU61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,27 +1950,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46171.5</v>
+        <v>46171.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46171.5</v>
+        <v>46171.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z13" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46171.54166666666</v>
+        <v>46171.5</v>
       </c>
     </row>
     <row r="14">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46171.54166666666</v>
+        <v>46171.5</v>
       </c>
     </row>
     <row r="15">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2825,31 +2825,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46171.54166666666</v>
+        <v>46171.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46171.5625</v>
+        <v>46171.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.75</v>
+        <v>5.07</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="U17" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.75</v>
+        <v>6.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="n">
         <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="O18" t="n">
-        <v>4.62</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>4.6</v>
+        <v>3.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.75</v>
+        <v>1.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>7.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46171.58333333334</v>
+        <v>46171.5625</v>
       </c>
     </row>
     <row r="21">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>7.41</v>
       </c>
       <c r="O21" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>3.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.73</v>
+        <v>1.05</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,65 +3905,65 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>4.66</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>5.16</v>
+        <v>3.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="R22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.5</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.8</v>
-      </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="V22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.67</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>9.449999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="O23" t="n">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="P23" t="n">
-        <v>1.28</v>
+        <v>5.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>2.99</v>
+        <v>4.9</v>
       </c>
       <c r="P24" t="n">
-        <v>4.19</v>
+        <v>1.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.04</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.5</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.23</v>
+        <v>1.15</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.31</v>
+        <v>3.86</v>
       </c>
       <c r="O26" t="n">
-        <v>2.72</v>
+        <v>3.68</v>
       </c>
       <c r="P26" t="n">
-        <v>3.34</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.17</v>
+        <v>4.53</v>
       </c>
       <c r="R26" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="T26" t="n">
-        <v>2.11</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>3.58</v>
+        <v>2.62</v>
       </c>
       <c r="V26" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF26" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,22 +4658,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>3.65</v>
+        <v>5.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="S27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.82</v>
+        <v>2.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.63</v>
+        <v>2.23</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>7.41</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.38</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O30" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="P30" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>3.44</v>
@@ -5201,10 +5201,10 @@
         <v>3.98</v>
       </c>
       <c r="V30" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1.14</v>
@@ -5231,10 +5231,10 @@
         <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5448,27 +5448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46171.60416666666</v>
+        <v>46171.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,19 +5654,19 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5687,31 +5687,31 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46171.60416666666</v>
+        <v>46171.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,61 +5972,61 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.67</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.7</v>
       </c>
       <c r="AG35" t="n">
         <v>2.05</v>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46171.625</v>
+        <v>46171.60416666666</v>
       </c>
     </row>
     <row r="36">
@@ -6084,27 +6084,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,81 +6131,81 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="O36" t="n">
-        <v>3.05</v>
+        <v>4.06</v>
       </c>
       <c r="P36" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB36" t="n">
         <v>2.1</v>
       </c>
-      <c r="S36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK36" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46171.65625</v>
+        <v>46171.625</v>
       </c>
     </row>
     <row r="37">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="P37" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S37" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T37" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="U37" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="V37" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.58</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="O38" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="P38" t="n">
-        <v>8.949999999999999</v>
+        <v>4.26</v>
       </c>
       <c r="Q38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF38" t="n">
         <v>1.75</v>
       </c>
-      <c r="R38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG38" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK38" t="n">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R40" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S40" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T40" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="U40" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W40" t="n">
         <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
         <v>1.95</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>2.14</v>
       </c>
       <c r="O41" t="n">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.73</v>
+        <v>2.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB41" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P43" t="n">
-        <v>4.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O44" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P44" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R44" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S44" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T44" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="U44" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W44" t="n">
         <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG44" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
         <v>1.95</v>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.2</v>
+        <v>1.27</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="R45" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="S45" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="T45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U45" t="n">
         <v>2.53</v>
       </c>
-      <c r="U45" t="n">
-        <v>3.15</v>
-      </c>
       <c r="V45" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.6</v>
+        <v>3.12</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46171.66666666666</v>
+        <v>46171.65625</v>
       </c>
     </row>
     <row r="46">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="S47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1.2</v>
       </c>
-      <c r="T47" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK47" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46171.67708333334</v>
+        <v>46171.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,77 +8198,77 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="O49" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="S49" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2.9</v>
       </c>
-      <c r="U49" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.3</v>
       </c>
       <c r="AK49" t="n">
         <v>1.4</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AU49" s="3" t="n">
-        <v>46171.79166666666</v>
+        <v>46171.67708333334</v>
       </c>
     </row>
     <row r="50">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46171.83333333334</v>
+        <v>46171.79166666666</v>
       </c>
     </row>
     <row r="51">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8787,27 +8787,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46171.875</v>
+        <v>46171.83333333334</v>
       </c>
     </row>
     <row r="54">
@@ -8951,22 +8951,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,19 +8993,19 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -9014,10 +9014,10 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W54" t="n">
         <v>0</v>
@@ -9026,31 +9026,31 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,22 +9110,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,22 +9428,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9746,22 +9746,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9900,27 +9900,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46171.875</v>
+        <v>46171.89583333334</v>
       </c>
     </row>
     <row r="61">
@@ -10059,27 +10059,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10209,1437 +10209,6 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Bijelo Brdo</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Croatia Zmijavci</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU62" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R63" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S63" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U63" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Racing Córdoba</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Ferro Carril Oeste</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U64" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU64" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Opatija</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Karlovac 1919</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Juventude</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>América Mineiro</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="O66" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P66" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R66" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U66" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Deportivo Madryn</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Acassuso</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P67" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S67" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U67" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Trajal Krusevac</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" s="3" t="n">
-        <v>46171.875</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Univ. Concepción</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O69" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P69" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R69" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="S69" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T69" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U69" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK69" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU69" s="3" t="n">
-        <v>46171.89583333334</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46171</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Real Monarchs</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Sporting KC II</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="3" t="n">
         <v>46171.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46171.27083333334</v>
+        <v>46171.16666666666</v>
       </c>
     </row>
     <row r="3">
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46171.29166666666</v>
+        <v>46171.27083333334</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46171.33333333334</v>
+        <v>46171.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3779,31 +3779,31 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="O23" t="n">
-        <v>4.66</v>
+        <v>3.25</v>
       </c>
       <c r="P23" t="n">
-        <v>5.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="V23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.67</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>9.449999999999999</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.04</v>
+        <v>1.49</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.95</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>4.95</v>
+        <v>4.66</v>
       </c>
       <c r="P25" t="n">
-        <v>1.49</v>
+        <v>5.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T25" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="U25" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
         <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
         <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.86</v>
+        <v>1.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.53</v>
+        <v>2.15</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.5</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P27" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.23</v>
+        <v>1.15</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,80 +4859,80 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>4.62</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.53</v>
+        <v>1.97</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T28" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="V28" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AC28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG28" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK28" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>4.47</v>
       </c>
       <c r="R29" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T29" t="n">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V29" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.4</v>
+        <v>7.41</v>
       </c>
       <c r="O30" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.68</v>
       </c>
-      <c r="S30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.93</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="P31" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="R31" t="n">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="S31" t="n">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="T31" t="n">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>3.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="P32" t="n">
-        <v>4.6</v>
+        <v>1.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.25</v>
+        <v>3.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,19 +5654,19 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5675,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5687,31 +5687,31 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,65 +6290,65 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O37" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="R37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG37" t="n">
         <v>2.1</v>
       </c>
-      <c r="S37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P38" t="n">
-        <v>4.26</v>
+        <v>2.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.36</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="Z38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.36</v>
       </c>
-      <c r="W38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="P39" t="n">
-        <v>2.88</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S39" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U39" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V39" t="n">
         <v>1.43</v>
       </c>
       <c r="W39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.11</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.57</v>
+        <v>3.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="P40" t="n">
         <v>1.73</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>4.3</v>
-      </c>
       <c r="Q40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O41" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P42" t="n">
-        <v>3.05</v>
+        <v>4.26</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="O43" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P43" t="n">
-        <v>1.73</v>
+        <v>4.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,80 +7403,80 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R44" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
         <v>1.3</v>
       </c>
-      <c r="T44" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK44" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,19 +7562,19 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.27</v>
+        <v>2.14</v>
       </c>
       <c r="O45" t="n">
-        <v>4.75</v>
+        <v>3.38</v>
       </c>
       <c r="P45" t="n">
-        <v>8.949999999999999</v>
+        <v>2.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="R45" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="S45" t="n">
         <v>1.32</v>
@@ -7592,34 +7592,34 @@
         <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB45" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE45" t="n">
         <v>1.14</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>3.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P48" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="S48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.16</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.19</v>
       </c>
       <c r="X48" t="n">
         <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB48" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF48" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG48" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R49" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="S49" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T49" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V49" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W49" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X49" t="n">
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R54" t="n">
         <v>2.15</v>
       </c>
-      <c r="O54" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P54" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.23</v>
-      </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U54" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V54" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="O55" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="P55" t="n">
-        <v>6.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R55" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S55" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T55" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U55" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="V55" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W55" t="n">
         <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="O56" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P56" t="n">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R56" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S56" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="V56" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC56" t="n">
         <v>2.8</v>
       </c>
-      <c r="AA56" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.92</v>
-      </c>
       <c r="AD56" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.93</v>
+        <v>1.5</v>
       </c>
       <c r="O57" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="P57" t="n">
-        <v>2.22</v>
+        <v>6.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S57" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="T57" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U57" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="V57" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="W57" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X57" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE57" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF57" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG57" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.69</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>5.07</v>
       </c>
       <c r="R18" t="n">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U18" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.7</v>
+        <v>6.35</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.71</v>
+        <v>1.1</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>3.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.07</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.1</v>
+        <v>1.71</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>5.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.53</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="S24" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="U24" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AK24" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>7.41</v>
       </c>
       <c r="O25" t="n">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
-        <v>5.16</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>3.7</v>
+        <v>4.66</v>
       </c>
       <c r="P26" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG26" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.95</v>
+        <v>1.78</v>
       </c>
       <c r="O27" t="n">
-        <v>4.95</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>1.49</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="S27" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.17</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.5</v>
       </c>
-      <c r="O28" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="P28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.47</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S29" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T29" t="n">
         <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V29" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.05</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5210,31 +5210,31 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>2.65</v>
+        <v>4.9</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF31" t="n">
         <v>2.04</v>
       </c>
-      <c r="U31" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AG31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>9.449999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="P32" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.65</v>
+        <v>2.23</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.71</v>
+        <v>2.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5657,61 +5657,61 @@
         <v>1.5</v>
       </c>
       <c r="O33" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P33" t="n">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="R33" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P37" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="O38" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.43</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
         <v>1.01</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z38" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.9</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="O39" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="P39" t="n">
-        <v>8.949999999999999</v>
+        <v>4.26</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1.75</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AG39" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AK39" t="n">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>2.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.22</v>
+        <v>1.27</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="P41" t="n">
-        <v>3.05</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="P42" t="n">
-        <v>4.26</v>
+        <v>1.73</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,80 +7562,80 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O45" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R45" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U45" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V45" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W45" t="n">
         <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB45" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK45" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="O55" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="P55" t="n">
-        <v>4.1</v>
+        <v>6.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S55" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U55" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="V55" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W55" t="n">
         <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,65 +9311,65 @@
         </is>
       </c>
       <c r="N56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P56" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R56" t="n">
         <v>2.15</v>
       </c>
-      <c r="O56" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P56" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R56" t="n">
-        <v>2.23</v>
-      </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U56" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="V56" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD56" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z56" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA56" t="n">
+      <c r="AE56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG56" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,58 +9470,58 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="P57" t="n">
-        <v>6.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S57" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="T57" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="U57" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="V57" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X57" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF57" t="n">
         <v>2.3</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK57" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,28 +9629,28 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="O58" t="n">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="P58" t="n">
-        <v>5.65</v>
+        <v>4.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S58" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T58" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U58" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="V58" t="n">
         <v>1.3</v>
@@ -9659,50 +9659,50 @@
         <v>1.02</v>
       </c>
       <c r="X58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE58" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AF58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z58" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK58" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O59" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q59" t="n">
         <v>2.7</v>
       </c>
-      <c r="P59" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>3.3</v>
-      </c>
       <c r="R59" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="S59" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="V59" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="W59" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.23</v>
+        <v>3.55</v>
       </c>
       <c r="AA59" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC59" t="n">
         <v>2.8</v>
       </c>
-      <c r="AB59" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>6</v>
-      </c>
       <c r="AD59" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE59" t="n">
         <v>1.11</v>
       </c>
-      <c r="AE59" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF59" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -1544,7 +1544,7 @@
         <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
         <v>1.09</v>
@@ -1553,10 +1553,10 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="AA7" t="n">
         <v>1.62</v>
@@ -1571,7 +1571,7 @@
         <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
         <v>1.53</v>
@@ -1593,7 +1593,7 @@
         <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2477,46 +2477,46 @@
         <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AC13" t="n">
         <v>2.06</v>
@@ -2525,13 +2525,13 @@
         <v>1.63</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
         <v>2.38</v>
@@ -3443,43 +3443,43 @@
         <v>2.28</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U19" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="V19" t="n">
         <v>1.44</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD19" t="n">
         <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF19" t="n">
         <v>1.63</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="O21" t="n">
-        <v>3.65</v>
+        <v>4.66</v>
       </c>
       <c r="P21" t="n">
-        <v>1.86</v>
+        <v>5.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.47</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T21" t="n">
-        <v>3.04</v>
+        <v>3.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
         <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.76</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.93</v>
+        <v>2.13</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="R22" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="T22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.5</v>
       </c>
-      <c r="U22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.57</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>5.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>2.67</v>
       </c>
       <c r="R23" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.35</v>
+        <v>2.49</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>2.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>4.57</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.5</v>
+        <v>9.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="U24" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="V24" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AC24" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>7.41</v>
+        <v>8.5</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>4.66</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>5.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>4.47</v>
       </c>
       <c r="R26" t="n">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T26" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="V26" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.13</v>
+        <v>2.93</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="O27" t="n">
         <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>5.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>4.65</v>
       </c>
       <c r="O29" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.39</v>
+        <v>1.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="R29" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="S29" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="U29" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.92</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>9.449999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="P31" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.65</v>
+        <v>2.23</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.71</v>
+        <v>2.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.75</v>
+        <v>5.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.04</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="O32" t="n">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="R32" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="S32" t="n">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>3.28</v>
       </c>
       <c r="U32" t="n">
-        <v>3.98</v>
+        <v>2.41</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.23</v>
+        <v>4.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.93</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.6</v>
+        <v>2.54</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5654,31 +5654,31 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="R33" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
         <v>1.2</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
         <v>2.14</v>
       </c>
       <c r="V33" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W33" t="n">
         <v>1.14</v>
@@ -5690,7 +5690,7 @@
         <v>1.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
         <v>1.47</v>
@@ -5699,7 +5699,7 @@
         <v>2.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD33" t="n">
         <v>1.62</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="O34" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P34" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U34" t="n">
-        <v>2.32</v>
+        <v>2.77</v>
       </c>
       <c r="V34" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="O35" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="R35" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.77</v>
+        <v>2.32</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,80 +6290,80 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="O37" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="P37" t="n">
-        <v>3.05</v>
+        <v>4.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK37" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="O38" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.96</v>
+        <v>3.22</v>
       </c>
       <c r="U38" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W38" t="n">
         <v>1.07</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB38" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.6</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P39" t="n">
-        <v>4.26</v>
+        <v>2.88</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R39" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S39" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="U39" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
         <v>1.01</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="O40" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="R40" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S40" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>3.18</v>
       </c>
       <c r="U40" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="V40" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.27</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>4.75</v>
+        <v>3.05</v>
       </c>
       <c r="P41" t="n">
-        <v>8.949999999999999</v>
+        <v>2.85</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="S41" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T41" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="U41" t="n">
-        <v>2.53</v>
+        <v>3.08</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK41" t="n">
-        <v>3.12</v>
+        <v>1.5</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,31 +7244,31 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="O43" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="P43" t="n">
-        <v>4.3</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="R43" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="S43" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T43" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="U43" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V43" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W43" t="n">
         <v>1.07</v>
@@ -7277,31 +7277,31 @@
         <v>1.04</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z43" t="n">
         <v>3.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD43" t="n">
         <v>1.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG43" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O44" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="P44" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R44" t="n">
         <v>2.25</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T44" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="U44" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V44" t="n">
         <v>1.43</v>
       </c>
       <c r="W44" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AA44" t="n">
         <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="O45" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.67</v>
+        <v>2.32</v>
       </c>
       <c r="O48" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P48" t="n">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R48" t="n">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="S48" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T48" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V48" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W48" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X48" t="n">
         <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z48" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="O49" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S49" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T49" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="U49" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V49" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W49" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X49" t="n">
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z49" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AB49" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF49" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF49" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG49" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="O54" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="P54" t="n">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="R54" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V54" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W54" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O55" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P55" t="n">
-        <v>6.55</v>
+        <v>5.65</v>
       </c>
       <c r="Q55" t="n">
         <v>2.1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S55" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T55" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="U55" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="V55" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W55" t="n">
         <v>1.02</v>
       </c>
       <c r="X55" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE55" t="n">
         <v>1.08</v>
       </c>
-      <c r="Y55" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF55" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,65 +9311,65 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.55</v>
+        <v>2.93</v>
       </c>
       <c r="O56" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="P56" t="n">
-        <v>5.65</v>
+        <v>2.22</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
         <v>2.15</v>
       </c>
       <c r="S56" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T56" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="U56" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="V56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD56" t="n">
         <v>1.3</v>
       </c>
-      <c r="W56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA56" t="n">
+      <c r="AE56" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG56" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK56" t="n">
-        <v>2.25</v>
+        <v>1.32</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,58 +9470,58 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="O57" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="P57" t="n">
-        <v>2.9</v>
+        <v>6.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="R57" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S57" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="T57" t="n">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="U57" t="n">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="V57" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="W57" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X57" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF57" t="n">
         <v>2.3</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="P58" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="S58" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="T58" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="U58" t="n">
-        <v>3.16</v>
+        <v>3.88</v>
       </c>
       <c r="V58" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X58" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE58" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y58" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF58" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="O59" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="P59" t="n">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="R59" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U59" t="n">
-        <v>2.45</v>
+        <v>3.32</v>
       </c>
       <c r="V59" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.8</v>
+        <v>4.14</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AG59" t="n">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>

--- a/jogos_2026-05-29.xlsx
+++ b/jogos_2026-05-29.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -2006,71 +2006,71 @@
         <v>3.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T10" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA10" t="n">
         <v>2.25</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.63</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2189,19 +2189,19 @@
         <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD11" t="n">
         <v>1.11</v>
@@ -2210,10 +2210,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2825,22 +2825,22 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>4.66</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>5.16</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="R21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.5</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
         <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S22" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK22" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4079,13 +4079,13 @@
         <v>2.04</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V23" t="n">
         <v>1.25</v>
@@ -4094,7 +4094,7 @@
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
         <v>1.42</v>
@@ -4115,7 +4115,7 @@
         <v>1.15</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
         <v>2.05</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>9.449999999999999</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>4.9</v>
+        <v>3.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.25</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.3</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,65 +4382,65 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>8.5</v>
+        <v>1.76</v>
       </c>
       <c r="O25" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>3.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.6</v>
+        <v>2.15</v>
       </c>
       <c r="R25" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U25" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="V25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.44</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG25" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.47</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="U26" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="W26" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.76</v>
+        <v>5.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2</v>
       </c>
-      <c r="AC26" t="n">
-        <v>2.93</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4817,22 +4817,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.65</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="P29" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.8</v>
+        <v>9.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="W29" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
         <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.37</v>
+        <v>4.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.22</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>10.6</v>
       </c>
       <c r="R30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF30" t="n">
         <v>2.2</v>
       </c>
-      <c r="S30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.11</v>
       </c>
-      <c r="AF30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P32" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.15</v>
+        <v>4.53</v>
       </c>
       <c r="R32" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="S32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T32" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="V32" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK32" t="n">
-        <v>2</v>
+        <v>1.23</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="P33" t="n">
-        <v>4.7</v>
+        <v>5.16</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
         <v>1.2</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U33" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="n">
         <v>1.25</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O34" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q34" t="n">
         <v>2.9</v>
@@ -5867,7 +5867,7 @@
         <v>1.11</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
         <v>2.05</v>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O36" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="P36" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q36" t="n">
         <v>2.15</v>
@@ -6146,34 +6146,34 @@
         <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U36" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" t="n">
         <v>4</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
         <v>2.75</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="P37" t="n">
-        <v>4.26</v>
+        <v>8.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S37" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U37" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O38" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="V38" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB38" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AC38" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O39" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P39" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6770,61 +6770,61 @@
         <v>1.73</v>
       </c>
       <c r="O40" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P40" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC40" t="n">
         <v>3.4</v>
       </c>
-      <c r="P40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF40" t="n">
         <v>1.75</v>
       </c>
       <c r="AG40" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="O41" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="R41" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S41" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T41" t="n">
-        <v>2.53</v>
+        <v>3.04</v>
       </c>
       <c r="U41" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W41" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE41" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>1.73</v>
+        <v>3.98</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>8.949999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="R43" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="S43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T43" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="U43" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="V43" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W43" t="n">
         <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB43" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK43" t="n">
-        <v>3.12</v>
+        <v>1.57</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.14</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.97</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P45" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.32</v>
+        <v>2.82</v>
       </c>
       <c r="O48" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P48" t="n">
-        <v>2.53</v>
+        <v>2.19</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="S48" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T48" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="U48" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V48" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W48" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X48" t="n">
         <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AB48" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF48" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF48" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AG48" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.82</v>
+        <v>2.32</v>
       </c>
       <c r="O49" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="R49" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="S49" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T49" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="U49" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V49" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W49" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X49" t="n">
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8360,13 +8360,13 @@
         <v>2.62</v>
       </c>
       <c r="O50" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P50" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
         <v>2.2</v>
@@ -8390,19 +8390,19 @@
         <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD50" t="n">
         <v>1.3</v>
@@ -8525,10 +8525,10 @@
         <v>3.74</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R51" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S51" t="n">
         <v>1.33</v>
@@ -8537,7 +8537,7 @@
         <v>2.88</v>
       </c>
       <c r="U51" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V51" t="n">
         <v>1.4</v>
@@ -8549,7 +8549,7 @@
         <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z51" t="n">
         <v>3.42</v>
@@ -8561,7 +8561,7 @@
         <v>1.87</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AD51" t="n">
         <v>1.29</v>
@@ -8573,7 +8573,7 @@
         <v>1.57</v>
       </c>
       <c r="AG51" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="O54" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P54" t="n">
-        <v>3.04</v>
+        <v>6.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="R54" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U54" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="V54" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z54" t="n">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.11</v>
+        <